--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ3"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -896,6 +896,121 @@
       <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125967357</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136950247</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99270</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Myckeedet, Mpd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>584076</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6964401</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136950247</t>
         </is>
       </c>
     </row>
@@ -903,6 +1018,7 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41118-2025 artfynd.xlsx
+++ b/artfynd/A 41118-2025 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>136950247</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
